--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/outcomes.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/claude-haiku-4-5/outcomes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,15 +469,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>MIPROC %CR (MI process coder)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>Reflection:Question (MITI)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>% Complex Reflections (MITI)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>% MI-Consistent (MITI)</t>
         </is>
@@ -513,18 +518,21 @@
         <v>2.352</v>
       </c>
       <c r="I2" t="n">
-        <v>0.633</v>
+        <v>0.613</v>
       </c>
       <c r="J2" t="n">
         <v>0.825</v>
       </c>
       <c r="K2" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.227</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.553</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.495</v>
       </c>
     </row>
@@ -558,18 +566,21 @@
         <v>2.148</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="J3" t="n">
         <v>0.581</v>
       </c>
       <c r="K3" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="L3" t="n">
         <v>1.175</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.306</v>
       </c>
     </row>
@@ -603,18 +614,21 @@
         <v>2.099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.612</v>
+        <v>0.58</v>
       </c>
       <c r="J4" t="n">
         <v>1.05</v>
       </c>
       <c r="K4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="L4" t="n">
         <v>1.47</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.232</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.768</v>
       </c>
     </row>
@@ -648,18 +662,21 @@
         <v>2.375</v>
       </c>
       <c r="I5" t="n">
-        <v>0.725</v>
+        <v>0.738</v>
       </c>
       <c r="J5" t="n">
         <v>0.628</v>
       </c>
       <c r="K5" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.56</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.658</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.382</v>
       </c>
     </row>
@@ -693,18 +710,21 @@
         <v>2.396</v>
       </c>
       <c r="I6" t="n">
-        <v>0.638</v>
+        <v>0.635</v>
       </c>
       <c r="J6" t="n">
         <v>0.747</v>
       </c>
       <c r="K6" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.905</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.451</v>
       </c>
     </row>
@@ -738,18 +758,21 @@
         <v>2.214</v>
       </c>
       <c r="I7" t="n">
-        <v>0.613</v>
+        <v>0.597</v>
       </c>
       <c r="J7" t="n">
         <v>0.581</v>
       </c>
       <c r="K7" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.827</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.593</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.277</v>
       </c>
     </row>
@@ -783,18 +806,21 @@
         <v>2.383</v>
       </c>
       <c r="I8" t="n">
-        <v>0.601</v>
+        <v>0.602</v>
       </c>
       <c r="J8" t="n">
         <v>0.407</v>
       </c>
       <c r="K8" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.423</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.34</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.414</v>
       </c>
     </row>
@@ -828,18 +854,21 @@
         <v>2.383</v>
       </c>
       <c r="I9" t="n">
-        <v>0.668</v>
+        <v>0.676</v>
       </c>
       <c r="J9" t="n">
         <v>0.58</v>
       </c>
       <c r="K9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.929</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.616</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.335</v>
       </c>
     </row>
